--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Centro Oriente.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Centro Oriente.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="U2KbS0inpLSuICYAW55+OF+j78TOCtHL0NA1uhveH6Q="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="UsXxOJCyouA6KLHAvgMKY6dxKYc9bqe5OxXuFdyF+1o="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Entidad</t>
   </si>
@@ -69,53 +69,10 @@
     <t>Subred Integrada De Servicios De Salud Centro Oriente</t>
   </si>
   <si>
-    <t>Plataforma Estratégica con enfoque en innovación</t>
-  </si>
-  <si>
-    <t>Misión; Eje Estratégico; Objetivo Estratégico; Manual de Investigación;</t>
-  </si>
-  <si>
-    <t>Misión: Somos la Subred Centro Oriente E.S.E., Institución Prestadora de Servicios de Salud en todos los niveles de complejidad, basados en evidencia científica, investigación y docencia; con un equipo humano comprometido y en constante formación. Ofrecemos una atención con Bondad, Segura y de Calidad a los pacientes y sus familias, mediante una gestión eficiente y transparente que garantiza la participación ciudadana y el respeto por los Derechos Humanos.
- Eje Estratégico:</t>
-  </si>
-  <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Rstpa pregunta 35.pdf</t>
-  </si>
-  <si>
-    <t>Jerarquía del instrumento</t>
-  </si>
-  <si>
-    <t>Pertinencia temática</t>
-  </si>
-  <si>
-    <t>Calidad y claridad del objetivo</t>
-  </si>
-  <si>
-    <t>Nivel de institucionalización</t>
-  </si>
-  <si>
-    <t>Soporte documental</t>
-  </si>
-  <si>
     <t>Plataforma Estratégica con enfoque en innovación y Manual de Investigación</t>
   </si>
   <si>
     <t>Misión; Eje Estratégico; Objetivo Estratégico; Politica; Manual de Investigación;</t>
-  </si>
-  <si>
-    <t>Misión: Somos la Subred Centro Oriente E.S.E., Institución Prestadora de Servicios de Salud en todos los niveles de complejidad, basados en evidencia científica, investigación y docencia; con un equipo humano comprometido y en constante formación. Ofrecemos una atención con Bondad, Segura y de Calidad a los pacientes y sus familias, mediante una gestión eficiente y transparente que garantiza la participación ciudadana y el respeto por los Derechos Humanos.
- Eje Estratégico. Fortalecimiento de la Gestión Clínica, la academia y la investigación institucional
- Objetivo Estratégico: Aumentar la generación de conocimiento aplicada al ciclo de atención en salud, mediante la conformación de redes de investigación con Instituciones reconocidas, que contribuyan al proceso formativo y de innovación institucional en el marco social.
- Politica: Gestión del conocimiento
- Indicador Plan de Desarrollo Institucional</t>
-  </si>
-  <si>
-    <t>Misión: Somos la Subred Centro Oriente E.S.E., Institución Prestadora de Servicios de Salud en todos los niveles de complejidad, basados en evidencia científica, investigación y docencia; con un equipo humano comprometido y en constante formación. Ofrecemos una atención con Bondad, Segura y de Calidad a los pacientes y sus familias, mediante una gestión eficiente y transparente que garantiza la participación ciudadana y el respeto por los Derechos Humanos.
- Eje Estratégico. Fortalecimiento de la Gestión Clínica, la academia y la investigación institucional
- Objetivo Estratégico: Aumentar la generación de conocimiento aplicada al ciclo de atención en salud, mediante la conformación de redes de investigación con Instituciones reconocidas, que contribuyan al proceso formativo y de innovación institucional en el marco social.
- Politica: Gestión del conocimiento
- Indicador Plan de Desarrollo Institucional
- Link:</t>
   </si>
   <si>
     <t>Misión: Somos la Subred Centro Oriente E.S.E., Institución Prestadora de Servicios de Salud en todos los niveles de complejidad, basados en evidencia científica, investigación y docencia; con un equipo humano comprometido y en constante formación. Ofrecemos una atención con Bondad, Segura y de Calidad a los pacientes y sus familias, mediante una gestión eficiente y transparente que garantiza la participación ciudadana y el respeto por los Derechos Humanos.
@@ -124,6 +81,24 @@
  Politica: Gestión del conocimiento
  Indicador Plan de Desarrollo Institucional
  Link: https://www.subredcentrooriente.gov.co/?q=transparencia/planeacion/metas-objetivos-indicadores</t>
+  </si>
+  <si>
+    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Rstpa pregunta 35.pdf</t>
+  </si>
+  <si>
+    <t>Jerarquía del instrumento</t>
+  </si>
+  <si>
+    <t>Pertinencia temática</t>
+  </si>
+  <si>
+    <t>Calidad y claridad del objetivo</t>
+  </si>
+  <si>
+    <t>Nivel de institucionalización</t>
+  </si>
+  <si>
+    <t>Soporte documental</t>
   </si>
 </sst>
 </file>
@@ -562,136 +537,9 @@
       </c>
       <c r="P2" s="4"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P3" s="4"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P4" s="4"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P5" s="4"/>
-    </row>
+    <row r="3" ht="14.25" customHeight="1"/>
+    <row r="4" ht="14.25" customHeight="1"/>
+    <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1"/>
     <row r="7" ht="14.25" customHeight="1"/>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -1684,9 +1532,6 @@
     <row r="995" ht="14.25" customHeight="1"/>
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
